--- a/prova_real/trimestre_05/resultado_T5.xlsx
+++ b/prova_real/trimestre_05/resultado_T5.xlsx
@@ -34,7 +34,7 @@
       <color rgb="00CCCCCC"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -49,6 +49,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="000D3B1F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="003B2D00"/>
       </patternFill>
     </fill>
     <fill>
@@ -69,7 +74,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -78,6 +83,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -445,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R32"/>
+  <dimension ref="A1:R37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -462,7 +470,7 @@
     <col width="18" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
     <col width="17" customWidth="1" min="16" max="16"/>
     <col width="16" customWidth="1" min="17" max="17"/>
     <col width="20" customWidth="1" min="18" max="18"/>
@@ -573,12 +581,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2025-02-21</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -590,10 +598,10 @@
         <v>56.5</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>16.4</v>
+        <v>15.27</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>79.04000000000001</v>
+        <v>82.41</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
@@ -616,22 +624,22 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>2.17</v>
+        <v>2.52</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>11.47</v>
+        <v>12.34</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.3602</v>
+        <v>0.1623</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>11111.11</v>
+        <v>10000</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>8782.219999999999</v>
+        <v>8241</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>19893.33</v>
+        <v>18241</v>
       </c>
     </row>
     <row r="3">
@@ -647,12 +655,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2025-02-21</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -661,13 +669,13 @@
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>66.09999999999999</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>9.41</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>32.27</v>
+        <v>39.42</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
@@ -690,22 +698,22 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>2.17</v>
+        <v>2.45</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>5.39</v>
+        <v>5.83</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.4309</v>
+        <v>0.3311</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>11111.11</v>
+        <v>10000</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>3585.56</v>
+        <v>3942</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>14696.67</v>
+        <v>13942</v>
       </c>
     </row>
     <row r="4">
@@ -773,13 +781,13 @@
         <v>-3.5009</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>11111.11</v>
+        <v>10000</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>3500</v>
+        <v>3150</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>14611.11</v>
+        <v>13150</v>
       </c>
     </row>
     <row r="5">
@@ -795,12 +803,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2025-02-21</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -812,10 +820,10 @@
         <v>56.5</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>5.98</v>
+        <v>6.15</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>23.03</v>
+        <v>22.23</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
@@ -838,22 +846,22 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>5.8</v>
+        <v>6.19</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>-0.55</v>
+        <v>-0.639</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>11111.11</v>
+        <v>10000</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>2558.89</v>
+        <v>2223</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>13670</v>
+        <v>12223</v>
       </c>
     </row>
     <row r="6">
@@ -864,32 +872,32 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>CMIG3</t>
+          <t>TOTS3</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2025-02-21</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>54.8</v>
+        <v>56.5</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>7.24</v>
+        <v>4.2</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>14.31</v>
+        <v>18.37</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
@@ -912,22 +920,22 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.73</v>
+        <v>5.09</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>5.62</v>
+        <v>13.55</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>-1.5479</v>
+        <v>-2.3606</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>11111.11</v>
+        <v>10000</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>1590</v>
+        <v>1837</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>12701.11</v>
+        <v>11837</v>
       </c>
     </row>
     <row r="7">
@@ -938,32 +946,32 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>TGMA3</t>
+          <t>CMIG3</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2025-02-21</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Previsibilidade Moderada</t>
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>56.5</v>
+        <v>54.8</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>10.39</v>
+        <v>6.96</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>14.02</v>
+        <v>17.01</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
@@ -986,22 +994,22 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.99</v>
+        <v>0.77</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>3.17</v>
+        <v>5.84</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>-0.2579</v>
+        <v>-0.1834</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>11111.11</v>
+        <v>10000</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>1557.78</v>
+        <v>1701</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>12668.89</v>
+        <v>11701</v>
       </c>
     </row>
     <row r="8">
@@ -1012,32 +1020,32 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>VLID3</t>
+          <t>TGMA3</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2025-02-21</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>54.8</v>
+        <v>56.5</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>9.710000000000001</v>
+        <v>10.27</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>10.95</v>
+        <v>14.57</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
@@ -1060,22 +1068,22 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.54</v>
+        <v>1.05</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>2.36</v>
+        <v>3.33</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.5279</v>
+        <v>-0.2216</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>11111.11</v>
+        <v>10000</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>1216.67</v>
+        <v>1457</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>12327.78</v>
+        <v>11457</v>
       </c>
     </row>
     <row r="9">
@@ -1086,32 +1094,32 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>BBSE3</t>
+          <t>VLID3</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2025-02-21</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Previsibilidade Moderada</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>56.5</v>
+        <v>54.8</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>4.21</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>3.51</v>
+        <v>12.55</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
@@ -1134,22 +1142,22 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>2.94</v>
+        <v>0.59</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>8.33</v>
+        <v>2.51</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>-5.7077</v>
+        <v>0.5288</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>11111.11</v>
+        <v>10000</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>390</v>
+        <v>1255</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>11501.11</v>
+        <v>11255</v>
       </c>
     </row>
     <row r="10">
@@ -1160,144 +1168,144 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
+          <t>CGRA4</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Previsibilidade Moderada</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>7.27</v>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>✅ SIM</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>✅ COMPRAR</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>0.1301</v>
+      </c>
+      <c r="P10" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="Q10" s="2" t="n">
+        <v>727</v>
+      </c>
+      <c r="R10" s="2" t="n">
+        <v>10727</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>T-5</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>PDGR3</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Muito Previsível</t>
         </is>
       </c>
-      <c r="F10" s="2" t="n">
-        <v>56.5</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>194.65</v>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>-62.4</v>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="F11" s="2" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>190.69</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>-72.8</v>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>QUEDA</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>❌ NÃO</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>✅ COMPRAR</t>
         </is>
       </c>
-      <c r="M10" s="2" t="n">
-        <v>2399.86</v>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>1738.11</v>
-      </c>
-      <c r="O10" s="2" t="n">
-        <v>-3890.6787</v>
-      </c>
-      <c r="P10" s="2" t="n">
-        <v>11111.11</v>
-      </c>
-      <c r="Q10" s="2" t="n">
-        <v>-6933.33</v>
-      </c>
-      <c r="R10" s="2" t="n">
-        <v>4177.78</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>T-5</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>CEAB3</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>Muito Previsível</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>58.1</v>
-      </c>
-      <c r="G11" s="3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="H11" s="3" t="n">
-        <v>80.18000000000001</v>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>✅ SIM</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t>❌ NÃO INDICADO</t>
-        </is>
-      </c>
-      <c r="M11" s="3" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="N11" s="3" t="n">
-        <v>18.59</v>
-      </c>
-      <c r="O11" s="3" t="n">
-        <v>-1.0425</v>
-      </c>
-      <c r="P11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" s="3" t="n">
-        <v>0</v>
+      <c r="M11" s="2" t="n">
+        <v>2318.49</v>
+      </c>
+      <c r="N11" s="2" t="n">
+        <v>1799.79</v>
+      </c>
+      <c r="O11" s="2" t="n">
+        <v>-4098.776</v>
+      </c>
+      <c r="P11" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="Q11" s="2" t="n">
+        <v>-7280</v>
+      </c>
+      <c r="R11" s="2" t="n">
+        <v>2720</v>
       </c>
     </row>
     <row r="12">
@@ -1308,32 +1316,32 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>TEND3</t>
+          <t>EMBJ3</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>2025-02-21</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Pouco Previsível</t>
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>61.3</v>
+        <v>53.2</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>3.39</v>
+        <v>14</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>36.57</v>
+        <v>6.68</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
@@ -1352,17 +1360,17 @@
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>❌ NÃO INDICADO</t>
+          <t>⚠️ OBSERVAR</t>
         </is>
       </c>
       <c r="M12" s="3" t="n">
-        <v>1.9</v>
+        <v>4.95</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>10.61</v>
+        <v>7.21</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>-0.3397</v>
+        <v>-0.7173</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>0</v>
@@ -1382,32 +1390,32 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>LAVV3</t>
+          <t>BBSE3</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>2025-02-21</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Pouco Previsível</t>
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>56.5</v>
+        <v>53.2</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.23</v>
+        <v>4.29</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>33.86</v>
+        <v>-0.05</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
@@ -1416,27 +1424,27 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>QUEDA</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>✅ SIM</t>
+          <t>❌ NÃO</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>❌ NÃO INDICADO</t>
+          <t>⚠️ OBSERVAR</t>
         </is>
       </c>
       <c r="M13" s="3" t="n">
-        <v>1.77</v>
+        <v>2.8</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>20.7</v>
+        <v>7.9</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>-6.2735</v>
+        <v>-5.6194</v>
       </c>
       <c r="P13" s="3" t="n">
         <v>0</v>
@@ -1456,17 +1464,17 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>NGRD3</t>
+          <t>POMO4</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>2025-02-21</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -1478,21 +1486,21 @@
         <v>53.2</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>-23.26</v>
+        <v>6.87</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>32.69</v>
+        <v>-0.96</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
           <t>QUEDA</t>
         </is>
       </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
           <t>❌ NÃO</t>
@@ -1500,1357 +1508,1727 @@
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
+          <t>⚠️ OBSERVAR</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="O14" s="3" t="n">
+        <v>-18.6074</v>
+      </c>
+      <c r="P14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>T-5</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>TEND3</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Muito Previsível</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>50.52</v>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>✅ SIM</t>
+        </is>
+      </c>
+      <c r="L15" s="4" t="inlineStr">
+        <is>
           <t>❌ NÃO INDICADO</t>
         </is>
       </c>
-      <c r="M14" s="3" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="N14" s="3" t="n">
-        <v>14.85</v>
-      </c>
-      <c r="O14" s="3" t="n">
-        <v>-2.6575</v>
-      </c>
-      <c r="P14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>T-5</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="M15" s="4" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="N15" s="4" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="O15" s="4" t="n">
+        <v>-0.2762</v>
+      </c>
+      <c r="P15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>T-5</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>DIRR3</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Muito Previsível</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>38.06</v>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>✅ SIM</t>
+        </is>
+      </c>
+      <c r="L16" s="4" t="inlineStr">
+        <is>
+          <t>❌ NÃO INDICADO</t>
+        </is>
+      </c>
+      <c r="M16" s="4" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="N16" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="O16" s="4" t="n">
+        <v>-2.8083</v>
+      </c>
+      <c r="P16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>T-5</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>LAVV3</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Muito Previsível</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>37.63</v>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>✅ SIM</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>❌ NÃO INDICADO</t>
+        </is>
+      </c>
+      <c r="M17" s="4" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="N17" s="4" t="n">
+        <v>20.58</v>
+      </c>
+      <c r="O17" s="4" t="n">
+        <v>-5.6629</v>
+      </c>
+      <c r="P17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>T-5</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>UNIP6</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>Muito Previsível</t>
         </is>
       </c>
-      <c r="F15" s="3" t="n">
+      <c r="F18" s="4" t="n">
         <v>58.1</v>
       </c>
-      <c r="G15" s="3" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="H15" s="3" t="n">
-        <v>31.72</v>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
+      <c r="G18" s="4" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>35.13</v>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
         <is>
           <t>✅ SIM</t>
         </is>
       </c>
-      <c r="L15" s="3" t="inlineStr">
+      <c r="L18" s="4" t="inlineStr">
         <is>
           <t>❌ NÃO INDICADO</t>
         </is>
       </c>
-      <c r="M15" s="3" t="n">
-        <v>6.68</v>
-      </c>
-      <c r="N15" s="3" t="n">
-        <v>14.14</v>
-      </c>
-      <c r="O15" s="3" t="n">
-        <v>-2.3863</v>
-      </c>
-      <c r="P15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>T-5</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="M18" s="4" t="n">
+        <v>7.13</v>
+      </c>
+      <c r="N18" s="4" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="O18" s="4" t="n">
+        <v>-2.8057</v>
+      </c>
+      <c r="P18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>T-5</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>NEOE3</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>Pouco Previsível</t>
         </is>
       </c>
-      <c r="F16" s="3" t="n">
+      <c r="F19" s="4" t="n">
         <v>53.2</v>
       </c>
-      <c r="G16" s="3" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="H16" s="3" t="n">
-        <v>28.76</v>
-      </c>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr">
+      <c r="G19" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>29.39</v>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
         <is>
           <t>✅ SIM</t>
         </is>
       </c>
-      <c r="L16" s="3" t="inlineStr">
+      <c r="L19" s="4" t="inlineStr">
         <is>
           <t>❌ NÃO INDICADO</t>
         </is>
       </c>
-      <c r="M16" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="N16" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="O16" s="3" t="n">
-        <v>-2.2451</v>
-      </c>
-      <c r="P16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>T-5</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>PINE4</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="M19" s="4" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="N19" s="4" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="O19" s="4" t="n">
+        <v>-2.3649</v>
+      </c>
+      <c r="P19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>T-5</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>SBSP3</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>Muito Previsível</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>59.7</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>25.98</v>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>✅ SIM</t>
+        </is>
+      </c>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>❌ NÃO INDICADO</t>
+        </is>
+      </c>
+      <c r="M20" s="4" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="N20" s="4" t="n">
+        <v>13.16</v>
+      </c>
+      <c r="O20" s="4" t="n">
+        <v>-2.4632</v>
+      </c>
+      <c r="P20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>T-5</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>VAMO3</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Previsibilidade Moderada</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>-40.91</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>20.05</v>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>❌ NÃO</t>
+        </is>
+      </c>
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>❌ NÃO INDICADO</t>
+        </is>
+      </c>
+      <c r="M21" s="4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="N21" s="4" t="n">
+        <v>29.13</v>
+      </c>
+      <c r="O21" s="4" t="n">
+        <v>-10.6755</v>
+      </c>
+      <c r="P21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>T-5</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>NGRD3</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>Muito Previsível</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>-24.8</v>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>16.12</v>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>❌ NÃO</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>❌ NÃO INDICADO</t>
+        </is>
+      </c>
+      <c r="M22" s="4" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="N22" s="4" t="n">
+        <v>17.84</v>
+      </c>
+      <c r="O22" s="4" t="n">
+        <v>-3.3615</v>
+      </c>
+      <c r="P22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>T-5</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>JSLG3</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Previsibilidade Moderada</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>-36.21</v>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>11.47</v>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>❌ NÃO</t>
+        </is>
+      </c>
+      <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t>❌ NÃO INDICADO</t>
+        </is>
+      </c>
+      <c r="M23" s="4" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="N23" s="4" t="n">
+        <v>31.31</v>
+      </c>
+      <c r="O23" s="4" t="n">
+        <v>-14.3704</v>
+      </c>
+      <c r="P23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>T-5</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>GFSA3</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
         <is>
           <t>Pouco Previsível</t>
         </is>
       </c>
-      <c r="F17" s="3" t="n">
+      <c r="F24" s="4" t="n">
         <v>53.2</v>
       </c>
-      <c r="G17" s="3" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="H17" s="3" t="n">
-        <v>26.57</v>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
+      <c r="G24" s="4" t="n">
+        <v>-117.27</v>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>10.91</v>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>❌ NÃO</t>
+        </is>
+      </c>
+      <c r="L24" s="4" t="inlineStr">
+        <is>
+          <t>❌ NÃO INDICADO</t>
+        </is>
+      </c>
+      <c r="M24" s="4" t="n">
+        <v>22.37</v>
+      </c>
+      <c r="N24" s="4" t="n">
+        <v>76.81</v>
+      </c>
+      <c r="O24" s="4" t="n">
+        <v>-12.5881</v>
+      </c>
+      <c r="P24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>T-5</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>CSMG3</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Muito Previsível</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="H25" s="4" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="K25" s="4" t="inlineStr">
         <is>
           <t>✅ SIM</t>
         </is>
       </c>
-      <c r="L17" s="3" t="inlineStr">
+      <c r="L25" s="4" t="inlineStr">
         <is>
           <t>❌ NÃO INDICADO</t>
         </is>
       </c>
-      <c r="M17" s="3" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="N17" s="3" t="n">
-        <v>5.44</v>
-      </c>
-      <c r="O17" s="3" t="n">
-        <v>-0.3634</v>
-      </c>
-      <c r="P17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>T-5</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>TOTS3</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="M25" s="4" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="N25" s="4" t="n">
+        <v>7.51</v>
+      </c>
+      <c r="O25" s="4" t="n">
+        <v>-0.08840000000000001</v>
+      </c>
+      <c r="P25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>T-5</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>AGRO3</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>Pouco Previsível</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>-5.78</v>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>❌ NÃO</t>
+        </is>
+      </c>
+      <c r="L26" s="4" t="inlineStr">
+        <is>
+          <t>❌ NÃO INDICADO</t>
+        </is>
+      </c>
+      <c r="M26" s="4" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="N26" s="4" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="O26" s="4" t="n">
+        <v>-0.1914</v>
+      </c>
+      <c r="P26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>T-5</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>CMIG4</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>Pouco Previsível</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="H27" s="4" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>✅ SIM</t>
+        </is>
+      </c>
+      <c r="L27" s="4" t="inlineStr">
+        <is>
+          <t>❌ NÃO INDICADO</t>
+        </is>
+      </c>
+      <c r="M27" s="4" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="N27" s="4" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="O27" s="4" t="n">
+        <v>-0.3034</v>
+      </c>
+      <c r="P27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>T-5</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>AERI3</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>Previsibilidade Moderada</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>-14.8</v>
+      </c>
+      <c r="H28" s="4" t="n">
+        <v>-0.47</v>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>✅ SIM</t>
+        </is>
+      </c>
+      <c r="L28" s="4" t="inlineStr">
+        <is>
+          <t>❌ NÃO INDICADO</t>
+        </is>
+      </c>
+      <c r="M28" s="4" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="N28" s="4" t="n">
+        <v>30.74</v>
+      </c>
+      <c r="O28" s="4" t="n">
+        <v>-15.8429</v>
+      </c>
+      <c r="P28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>T-5</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>POSI3</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>Pouco Previsível</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>-14.2</v>
+      </c>
+      <c r="H29" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>✅ SIM</t>
+        </is>
+      </c>
+      <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>❌ NÃO INDICADO</t>
+        </is>
+      </c>
+      <c r="M29" s="4" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="N29" s="4" t="n">
+        <v>11.93</v>
+      </c>
+      <c r="O29" s="4" t="n">
+        <v>-4.4947</v>
+      </c>
+      <c r="P29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>T-5</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>GGBR3</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>Pouco Previsível</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>-5.11</v>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>❌ NÃO</t>
+        </is>
+      </c>
+      <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>❌ NÃO INDICADO</t>
+        </is>
+      </c>
+      <c r="M30" s="4" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="N30" s="4" t="n">
+        <v>16.05</v>
+      </c>
+      <c r="O30" s="4" t="n">
+        <v>-16.8894</v>
+      </c>
+      <c r="P30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>T-5</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>DMVF3</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>Previsibilidade Moderada</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>-13.78</v>
+      </c>
+      <c r="H31" s="4" t="n">
+        <v>-6.57</v>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="K31" s="4" t="inlineStr">
+        <is>
+          <t>✅ SIM</t>
+        </is>
+      </c>
+      <c r="L31" s="4" t="inlineStr">
+        <is>
+          <t>❌ NÃO INDICADO</t>
+        </is>
+      </c>
+      <c r="M31" s="4" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="N31" s="4" t="n">
+        <v>8.960000000000001</v>
+      </c>
+      <c r="O31" s="4" t="n">
+        <v>-1.967</v>
+      </c>
+      <c r="P31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>T-5</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>BRKM5</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
         <is>
           <t>Muito Previsível</t>
         </is>
       </c>
-      <c r="F18" s="3" t="n">
-        <v>59.7</v>
-      </c>
-      <c r="G18" s="3" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="H18" s="3" t="n">
-        <v>24.88</v>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
+      <c r="F32" s="4" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>-24.37</v>
+      </c>
+      <c r="H32" s="4" t="n">
+        <v>-8.779999999999999</v>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="inlineStr">
         <is>
           <t>✅ SIM</t>
         </is>
       </c>
-      <c r="L18" s="3" t="inlineStr">
+      <c r="L32" s="4" t="inlineStr">
         <is>
           <t>❌ NÃO INDICADO</t>
         </is>
       </c>
-      <c r="M18" s="3" t="n">
-        <v>5.18</v>
-      </c>
-      <c r="N18" s="3" t="n">
-        <v>14.02</v>
-      </c>
-      <c r="O18" s="3" t="n">
-        <v>-2.997</v>
-      </c>
-      <c r="P18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>T-5</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>DIRR3</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="M32" s="4" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="N32" s="4" t="n">
+        <v>8.369999999999999</v>
+      </c>
+      <c r="O32" s="4" t="n">
+        <v>-1.8974</v>
+      </c>
+      <c r="P32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>T-5</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>USIM5</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>Previsibilidade Moderada</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>-6.75</v>
+      </c>
+      <c r="H33" s="4" t="n">
+        <v>-12.9</v>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="K33" s="4" t="inlineStr">
+        <is>
+          <t>✅ SIM</t>
+        </is>
+      </c>
+      <c r="L33" s="4" t="inlineStr">
+        <is>
+          <t>❌ NÃO INDICADO</t>
+        </is>
+      </c>
+      <c r="M33" s="4" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="N33" s="4" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="O33" s="4" t="n">
+        <v>-1.4101</v>
+      </c>
+      <c r="P33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>T-5</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>ONCO3</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
         <is>
           <t>Muito Previsível</t>
         </is>
       </c>
-      <c r="F19" s="3" t="n">
-        <v>61.3</v>
-      </c>
-      <c r="G19" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H19" s="3" t="n">
-        <v>24.81</v>
-      </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="K19" s="3" t="inlineStr">
+      <c r="F34" s="4" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>-139.44</v>
+      </c>
+      <c r="H34" s="4" t="n">
+        <v>-13.1</v>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="K34" s="4" t="inlineStr">
         <is>
           <t>✅ SIM</t>
         </is>
       </c>
-      <c r="L19" s="3" t="inlineStr">
+      <c r="L34" s="4" t="inlineStr">
         <is>
           <t>❌ NÃO INDICADO</t>
         </is>
       </c>
-      <c r="M19" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="N19" s="3" t="n">
-        <v>15.73</v>
-      </c>
-      <c r="O19" s="3" t="n">
-        <v>-3.0616</v>
-      </c>
-      <c r="P19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>T-5</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>SBSP3</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>Muito Previsível</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>59.7</v>
-      </c>
-      <c r="G20" s="3" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="H20" s="3" t="n">
-        <v>24.74</v>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="inlineStr">
+      <c r="M34" s="4" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="N34" s="4" t="n">
+        <v>91.48</v>
+      </c>
+      <c r="O34" s="4" t="n">
+        <v>-150.9031</v>
+      </c>
+      <c r="P34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>T-5</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>SEQL3</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>Pouco Previsível</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="G35" s="4" t="n">
+        <v>-92.84</v>
+      </c>
+      <c r="H35" s="4" t="n">
+        <v>-13.66</v>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="K35" s="4" t="inlineStr">
         <is>
           <t>✅ SIM</t>
         </is>
       </c>
-      <c r="L20" s="3" t="inlineStr">
+      <c r="L35" s="4" t="inlineStr">
         <is>
           <t>❌ NÃO INDICADO</t>
         </is>
       </c>
-      <c r="M20" s="3" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="N20" s="3" t="n">
-        <v>12.43</v>
-      </c>
-      <c r="O20" s="3" t="n">
-        <v>-2.2379</v>
-      </c>
-      <c r="P20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>T-5</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>GFSA3</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="M35" s="4" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="N35" s="4" t="n">
+        <v>50.38</v>
+      </c>
+      <c r="O35" s="4" t="n">
+        <v>-259.3709</v>
+      </c>
+      <c r="P35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>T-5</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>BBAS3</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
         <is>
           <t>Pouco Previsível</t>
         </is>
       </c>
-      <c r="F21" s="3" t="n">
+      <c r="F36" s="4" t="n">
         <v>53.2</v>
       </c>
-      <c r="G21" s="3" t="n">
-        <v>-122.27</v>
-      </c>
-      <c r="H21" s="3" t="n">
-        <v>13.64</v>
-      </c>
-      <c r="I21" s="3" t="inlineStr">
+      <c r="G36" s="4" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="H36" s="4" t="n">
+        <v>-14.59</v>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
         <is>
           <t>QUEDA</t>
         </is>
       </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t>❌ NÃO</t>
-        </is>
-      </c>
-      <c r="L21" s="3" t="inlineStr">
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="K36" s="4" t="inlineStr">
+        <is>
+          <t>✅ SIM</t>
+        </is>
+      </c>
+      <c r="L36" s="4" t="inlineStr">
         <is>
           <t>❌ NÃO INDICADO</t>
         </is>
       </c>
-      <c r="M21" s="3" t="n">
-        <v>22.67</v>
-      </c>
-      <c r="N21" s="3" t="n">
-        <v>77.48999999999999</v>
-      </c>
-      <c r="O21" s="3" t="n">
-        <v>-12.9027</v>
-      </c>
-      <c r="P21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>T-5</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>CSMG3</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>Muito Previsível</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>56.5</v>
-      </c>
-      <c r="G22" s="3" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="H22" s="3" t="n">
-        <v>11.13</v>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
+      <c r="M36" s="4" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="N36" s="4" t="n">
+        <v>8.69</v>
+      </c>
+      <c r="O36" s="4" t="n">
+        <v>-2.05</v>
+      </c>
+      <c r="P36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>T-5</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>AGXY3</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>Previsibilidade Moderada</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="G37" s="4" t="n">
+        <v>-108.16</v>
+      </c>
+      <c r="H37" s="4" t="n">
+        <v>-23.15</v>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="K37" s="4" t="inlineStr">
         <is>
           <t>✅ SIM</t>
         </is>
       </c>
-      <c r="L22" s="3" t="inlineStr">
+      <c r="L37" s="4" t="inlineStr">
         <is>
           <t>❌ NÃO INDICADO</t>
         </is>
       </c>
-      <c r="M22" s="3" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="N22" s="3" t="n">
-        <v>7.31</v>
-      </c>
-      <c r="O22" s="3" t="n">
-        <v>-0.1916</v>
-      </c>
-      <c r="P22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>T-5</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>JSLG3</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>Pouco Previsível</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="n">
-        <v>53.2</v>
-      </c>
-      <c r="G23" s="3" t="n">
-        <v>-36.62</v>
-      </c>
-      <c r="H23" s="3" t="n">
-        <v>10.24</v>
-      </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t>QUEDA</t>
-        </is>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="K23" s="3" t="inlineStr">
-        <is>
-          <t>❌ NÃO</t>
-        </is>
-      </c>
-      <c r="L23" s="3" t="inlineStr">
-        <is>
-          <t>❌ NÃO INDICADO</t>
-        </is>
-      </c>
-      <c r="M23" s="3" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="N23" s="3" t="n">
-        <v>30.87</v>
-      </c>
-      <c r="O23" s="3" t="n">
-        <v>-14.1375</v>
-      </c>
-      <c r="P23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>T-5</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>CMIG4</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>Pouco Previsível</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="n">
-        <v>53.2</v>
-      </c>
-      <c r="G24" s="3" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="H24" s="3" t="n">
-        <v>5.44</v>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>✅ SIM</t>
-        </is>
-      </c>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t>❌ NÃO INDICADO</t>
-        </is>
-      </c>
-      <c r="M24" s="3" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="N24" s="3" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="O24" s="3" t="n">
-        <v>-0.6091</v>
-      </c>
-      <c r="P24" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>T-5</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>AGRO3</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>Previsibilidade Moderada</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="n">
-        <v>54.8</v>
-      </c>
-      <c r="G25" s="3" t="n">
-        <v>-5.46</v>
-      </c>
-      <c r="H25" s="3" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t>QUEDA</t>
-        </is>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="inlineStr">
-        <is>
-          <t>❌ NÃO</t>
-        </is>
-      </c>
-      <c r="L25" s="3" t="inlineStr">
-        <is>
-          <t>❌ NÃO INDICADO</t>
-        </is>
-      </c>
-      <c r="M25" s="3" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="N25" s="3" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="O25" s="3" t="n">
-        <v>-0.1958</v>
-      </c>
-      <c r="P25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>T-5</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>ONCO3</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>Muito Previsível</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="n">
-        <v>56.5</v>
-      </c>
-      <c r="G26" s="3" t="n">
-        <v>-179.35</v>
-      </c>
-      <c r="H26" s="3" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>QUEDA</t>
-        </is>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t>❌ NÃO</t>
-        </is>
-      </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t>❌ NÃO INDICADO</t>
-        </is>
-      </c>
-      <c r="M26" s="3" t="n">
-        <v>5.24</v>
-      </c>
-      <c r="N26" s="3" t="n">
-        <v>97.72</v>
-      </c>
-      <c r="O26" s="3" t="n">
-        <v>-172.3388</v>
-      </c>
-      <c r="P26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>T-5</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>GGBR3</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>Muito Previsível</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>56.5</v>
-      </c>
-      <c r="G27" s="3" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="H27" s="3" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="K27" s="3" t="inlineStr">
-        <is>
-          <t>✅ SIM</t>
-        </is>
-      </c>
-      <c r="L27" s="3" t="inlineStr">
-        <is>
-          <t>❌ NÃO INDICADO</t>
-        </is>
-      </c>
-      <c r="M27" s="3" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="N27" s="3" t="n">
-        <v>17.35</v>
-      </c>
-      <c r="O27" s="3" t="n">
-        <v>-19.9623</v>
-      </c>
-      <c r="P27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>T-5</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>VAMO3</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>Muito Previsível</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>59.7</v>
-      </c>
-      <c r="G28" s="3" t="n">
-        <v>-41.94</v>
-      </c>
-      <c r="H28" s="3" t="n">
-        <v>-1.95</v>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t>QUEDA</t>
-        </is>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>QUEDA</t>
-        </is>
-      </c>
-      <c r="K28" s="3" t="inlineStr">
-        <is>
-          <t>✅ SIM</t>
-        </is>
-      </c>
-      <c r="L28" s="3" t="inlineStr">
-        <is>
-          <t>❌ NÃO INDICADO</t>
-        </is>
-      </c>
-      <c r="M28" s="3" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="N28" s="3" t="n">
-        <v>28.61</v>
-      </c>
-      <c r="O28" s="3" t="n">
-        <v>-10.6736</v>
-      </c>
-      <c r="P28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>T-5</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>DMVF3</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>Previsibilidade Moderada</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>54.8</v>
-      </c>
-      <c r="G29" s="3" t="n">
-        <v>-14.59</v>
-      </c>
-      <c r="H29" s="3" t="n">
-        <v>-10.08</v>
-      </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t>QUEDA</t>
-        </is>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>QUEDA</t>
-        </is>
-      </c>
-      <c r="K29" s="3" t="inlineStr">
-        <is>
-          <t>✅ SIM</t>
-        </is>
-      </c>
-      <c r="L29" s="3" t="inlineStr">
-        <is>
-          <t>❌ NÃO INDICADO</t>
-        </is>
-      </c>
-      <c r="M29" s="3" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="N29" s="3" t="n">
-        <v>10.03</v>
-      </c>
-      <c r="O29" s="3" t="n">
-        <v>-2.5228</v>
-      </c>
-      <c r="P29" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>T-5</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>BRKM5</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>Muito Previsível</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="n">
-        <v>61.3</v>
-      </c>
-      <c r="G30" s="3" t="n">
-        <v>-23.47</v>
-      </c>
-      <c r="H30" s="3" t="n">
-        <v>-11.05</v>
-      </c>
-      <c r="I30" s="3" t="inlineStr">
-        <is>
-          <t>QUEDA</t>
-        </is>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>QUEDA</t>
-        </is>
-      </c>
-      <c r="K30" s="3" t="inlineStr">
-        <is>
-          <t>✅ SIM</t>
-        </is>
-      </c>
-      <c r="L30" s="3" t="inlineStr">
-        <is>
-          <t>❌ NÃO INDICADO</t>
-        </is>
-      </c>
-      <c r="M30" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="N30" s="3" t="n">
-        <v>7.53</v>
-      </c>
-      <c r="O30" s="3" t="n">
-        <v>-0.7207</v>
-      </c>
-      <c r="P30" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>T-5</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>AERI3</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>Previsibilidade Moderada</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="n">
-        <v>54.8</v>
-      </c>
-      <c r="G31" s="3" t="n">
-        <v>-11.23</v>
-      </c>
-      <c r="H31" s="3" t="n">
-        <v>-12.73</v>
-      </c>
-      <c r="I31" s="3" t="inlineStr">
-        <is>
-          <t>QUEDA</t>
-        </is>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>QUEDA</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t>✅ SIM</t>
-        </is>
-      </c>
-      <c r="L31" s="3" t="inlineStr">
-        <is>
-          <t>❌ NÃO INDICADO</t>
-        </is>
-      </c>
-      <c r="M31" s="3" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="N31" s="3" t="n">
-        <v>38.2</v>
-      </c>
-      <c r="O31" s="3" t="n">
-        <v>-21.3856</v>
-      </c>
-      <c r="P31" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>T-5</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>RADL3</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>Pouco Previsível</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="n">
-        <v>53.2</v>
-      </c>
-      <c r="G32" s="3" t="n">
-        <v>-18.81</v>
-      </c>
-      <c r="H32" s="3" t="n">
-        <v>-20.79</v>
-      </c>
-      <c r="I32" s="3" t="inlineStr">
-        <is>
-          <t>QUEDA</t>
-        </is>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>QUEDA</t>
-        </is>
-      </c>
-      <c r="K32" s="3" t="inlineStr">
-        <is>
-          <t>✅ SIM</t>
-        </is>
-      </c>
-      <c r="L32" s="3" t="inlineStr">
-        <is>
-          <t>❌ NÃO INDICADO</t>
-        </is>
-      </c>
-      <c r="M32" s="3" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="N32" s="3" t="n">
-        <v>8.76</v>
-      </c>
-      <c r="O32" s="3" t="n">
-        <v>0.1475</v>
-      </c>
-      <c r="P32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" s="3" t="n">
+      <c r="M37" s="4" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="N37" s="4" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="O37" s="4" t="n">
+        <v>-49.8252</v>
+      </c>
+      <c r="P37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2865,7 +3243,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R10"/>
+  <dimension ref="A1:R11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2882,7 +3260,7 @@
     <col width="13" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
     <col width="17" customWidth="1" min="16" max="16"/>
     <col width="16" customWidth="1" min="17" max="17"/>
     <col width="20" customWidth="1" min="18" max="18"/>
@@ -2993,12 +3371,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2025-02-21</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -3010,10 +3388,10 @@
         <v>56.5</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>16.4</v>
+        <v>15.27</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>79.04000000000001</v>
+        <v>82.41</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
@@ -3036,22 +3414,22 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>2.17</v>
+        <v>2.52</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>11.47</v>
+        <v>12.34</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.3602</v>
+        <v>0.1623</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>11111.11</v>
+        <v>10000</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>8782.219999999999</v>
+        <v>8241</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>19893.33</v>
+        <v>18241</v>
       </c>
     </row>
     <row r="3">
@@ -3067,12 +3445,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2025-02-21</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -3081,13 +3459,13 @@
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>66.09999999999999</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>9.41</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>32.27</v>
+        <v>39.42</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
@@ -3110,22 +3488,22 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>2.17</v>
+        <v>2.45</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>5.39</v>
+        <v>5.83</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.4309</v>
+        <v>0.3311</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>11111.11</v>
+        <v>10000</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>3585.56</v>
+        <v>3942</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>14696.67</v>
+        <v>13942</v>
       </c>
     </row>
     <row r="4">
@@ -3193,13 +3571,13 @@
         <v>-3.5009</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>11111.11</v>
+        <v>10000</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>3500</v>
+        <v>3150</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>14611.11</v>
+        <v>13150</v>
       </c>
     </row>
     <row r="5">
@@ -3215,12 +3593,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2025-02-21</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -3232,10 +3610,10 @@
         <v>56.5</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>5.98</v>
+        <v>6.15</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>23.03</v>
+        <v>22.23</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
@@ -3258,22 +3636,22 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>5.8</v>
+        <v>6.19</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>-0.55</v>
+        <v>-0.639</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>11111.11</v>
+        <v>10000</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>2558.89</v>
+        <v>2223</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>13670</v>
+        <v>12223</v>
       </c>
     </row>
     <row r="6">
@@ -3284,32 +3662,32 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>CMIG3</t>
+          <t>TOTS3</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2025-02-21</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>54.8</v>
+        <v>56.5</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>7.24</v>
+        <v>4.2</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>14.31</v>
+        <v>18.37</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
@@ -3332,22 +3710,22 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.73</v>
+        <v>5.09</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>5.62</v>
+        <v>13.55</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>-1.5479</v>
+        <v>-2.3606</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>11111.11</v>
+        <v>10000</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>1590</v>
+        <v>1837</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>12701.11</v>
+        <v>11837</v>
       </c>
     </row>
     <row r="7">
@@ -3358,32 +3736,32 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>TGMA3</t>
+          <t>CMIG3</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2025-02-21</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Previsibilidade Moderada</t>
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>56.5</v>
+        <v>54.8</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>10.39</v>
+        <v>6.96</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>14.02</v>
+        <v>17.01</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
@@ -3406,22 +3784,22 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.99</v>
+        <v>0.77</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>3.17</v>
+        <v>5.84</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>-0.2579</v>
+        <v>-0.1834</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>11111.11</v>
+        <v>10000</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>1557.78</v>
+        <v>1701</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>12668.89</v>
+        <v>11701</v>
       </c>
     </row>
     <row r="8">
@@ -3432,32 +3810,32 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>VLID3</t>
+          <t>TGMA3</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2025-02-21</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>54.8</v>
+        <v>56.5</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>9.710000000000001</v>
+        <v>10.27</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>10.95</v>
+        <v>14.57</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
@@ -3480,22 +3858,22 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.54</v>
+        <v>1.05</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>2.36</v>
+        <v>3.33</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.5279</v>
+        <v>-0.2216</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>11111.11</v>
+        <v>10000</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>1216.67</v>
+        <v>1457</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>12327.78</v>
+        <v>11457</v>
       </c>
     </row>
     <row r="9">
@@ -3506,32 +3884,32 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>BBSE3</t>
+          <t>VLID3</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2025-02-21</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Previsibilidade Moderada</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>56.5</v>
+        <v>54.8</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>4.21</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>3.51</v>
+        <v>12.55</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
@@ -3554,22 +3932,22 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>2.94</v>
+        <v>0.59</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>8.33</v>
+        <v>2.51</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>-5.7077</v>
+        <v>0.5288</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>11111.11</v>
+        <v>10000</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>390</v>
+        <v>1255</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>11501.11</v>
+        <v>11255</v>
       </c>
     </row>
     <row r="10">
@@ -3580,70 +3958,144 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
+          <t>CGRA4</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Previsibilidade Moderada</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>7.27</v>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>✅ SIM</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>✅ COMPRAR</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>0.1301</v>
+      </c>
+      <c r="P10" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="Q10" s="2" t="n">
+        <v>727</v>
+      </c>
+      <c r="R10" s="2" t="n">
+        <v>10727</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>T-5</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>PDGR3</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Muito Previsível</t>
         </is>
       </c>
-      <c r="F10" s="2" t="n">
-        <v>56.5</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>194.65</v>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>-62.4</v>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="F11" s="2" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>190.69</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>-72.8</v>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>QUEDA</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>❌ NÃO</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>✅ COMPRAR</t>
         </is>
       </c>
-      <c r="M10" s="2" t="n">
-        <v>2399.86</v>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>1738.11</v>
-      </c>
-      <c r="O10" s="2" t="n">
-        <v>-3890.6787</v>
-      </c>
-      <c r="P10" s="2" t="n">
-        <v>11111.11</v>
-      </c>
-      <c r="Q10" s="2" t="n">
-        <v>-6933.33</v>
-      </c>
-      <c r="R10" s="2" t="n">
-        <v>4177.78</v>
+      <c r="M11" s="2" t="n">
+        <v>2318.49</v>
+      </c>
+      <c r="N11" s="2" t="n">
+        <v>1799.79</v>
+      </c>
+      <c r="O11" s="2" t="n">
+        <v>-4098.776</v>
+      </c>
+      <c r="P11" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="Q11" s="2" t="n">
+        <v>-7280</v>
+      </c>
+      <c r="R11" s="2" t="n">
+        <v>2720</v>
       </c>
     </row>
   </sheetData>
